--- a/output/pdf_financials_xlsx/NKW.H.xlsx
+++ b/output/pdf_financials_xlsx/NKW.H.xlsx
@@ -1107,13 +1107,13 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.002045</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.001932</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.001469</v>
       </c>
     </row>
     <row r="13">
@@ -2107,13 +2107,13 @@
         <v>-0.401902</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.337928</v>
+        <v>-0.339973</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.604058</v>
+        <v>0.6021260000000001</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>0.900206</v>
+        <v>0.898737</v>
       </c>
     </row>
     <row r="28">
@@ -2231,13 +2231,13 @@
         <v>-0.401902</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.337928</v>
+        <v>-0.339973</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.604058</v>
+        <v>0.6021260000000001</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.900206</v>
+        <v>0.898737</v>
       </c>
     </row>
     <row r="30">
@@ -2522,13 +2522,13 @@
         <v>0.049926</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.035111</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.013448</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.6779849999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2642,13 +2642,13 @@
         <v>0.049926</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.035111</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.013448</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.6779849999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3362,13 +3362,13 @@
         <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.036009</v>
+        <v>0.000898</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.014922</v>
+        <v>0.001474</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.679459</v>
+        <v>0.001474</v>
       </c>
     </row>
     <row r="49">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -36827,7 +36827,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">

--- a/output/pdf_financials_xlsx/NKW.H.xlsx
+++ b/output/pdf_financials_xlsx/NKW.H.xlsx
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-4.01</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-4.01</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -6937,13 +6937,13 @@
         </is>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0.043124</v>
+        <v>0.197124</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0.021562</v>
+        <v>0.181562</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q107" s="3" t="n">
         <v>0</v>
@@ -7079,16 +7079,16 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.123504</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.168855</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.009801000000000001</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.009903</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
@@ -7126,10 +7126,10 @@
         <v>0</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.014869</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.011846</v>
       </c>
     </row>
     <row r="111">
@@ -7379,10 +7379,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.544852</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.544852</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -20410,7 +20410,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -23155,7 +23159,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -23252,7 +23260,11 @@
           <t>Share based compensation expense</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -24103,7 +24115,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -25299,7 +25315,11 @@
           <t>Share based compensation expense (note 4)</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -25703,7 +25723,11 @@
           <t>Share based compensation expense (note 6)</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -28164,7 +28188,11 @@
           <t>Proceeds of private placement</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -28368,7 +28396,11 @@
           <t>Proceeds of private placement (note 6(a))</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -28976,7 +29008,11 @@
           <t>Proceeds of Private Placement (note 6(c))</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -29382,7 +29418,11 @@
           <t>Proceeds of Private Placement (note 7(c))</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -30798,7 +30838,11 @@
           <t>Accretion 45,351</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -31796,7 +31840,11 @@
           <t>Future income tax recovery -</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E233" s="5" t="n">
         <v>-4.01</v>
       </c>
@@ -32491,7 +32539,11 @@
           <t>Proceeds on sale of investments -</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E240" s="5" t="n">
         <v>0.544852</v>
       </c>
@@ -34103,7 +34155,11 @@
           <t>Accretion 43,192</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E256" s="5" t="n">
         <v>0.123504</v>
       </c>
@@ -46781,7 +46837,11 @@
           <t>Future income tax recovery -</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E384" s="5" t="n">
         <v>4.01</v>
       </c>
